--- a/FFL_Data.xlsx
+++ b/FFL_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axelrade\Downloads\FFL-Dash-2025-main\FFL-Dash-2025-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edenaxelrad/Desktop/FFL-Dash-2025-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427EE618-916E-4ED7-98CA-6670AEB74EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BB9905-3458-BE45-876F-2C6BC6C65651}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 Results" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="37">
   <si>
     <t>Points Against</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Moonies of Io</t>
+  </si>
+  <si>
+    <t>Week 8</t>
   </si>
 </sst>
 </file>
@@ -204,9 +207,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -244,7 +247,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -350,7 +353,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -492,7 +495,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -501,15 +504,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657FD601-2028-0A4F-BA12-553C96356FC4}">
   <dimension ref="A1:E169"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -526,7 +529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -540,7 +543,7 @@
         <v>124.56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -554,7 +557,7 @@
         <v>76.12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -568,7 +571,7 @@
         <v>108.82</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -582,7 +585,7 @@
         <v>101.22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -596,7 +599,7 @@
         <v>56.94</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -610,7 +613,7 @@
         <v>122.52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -624,7 +627,7 @@
         <v>101.88</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -638,7 +641,7 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -652,7 +655,7 @@
         <v>120.96</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -666,7 +669,7 @@
         <v>93.52</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -680,7 +683,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -694,7 +697,7 @@
         <v>99.48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -708,7 +711,7 @@
         <v>93.72</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -722,7 +725,7 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -736,7 +739,7 @@
         <v>128.44</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -750,7 +753,7 @@
         <v>109.18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -764,7 +767,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -778,7 +781,7 @@
         <v>92.18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -792,7 +795,7 @@
         <v>99.82</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -806,7 +809,7 @@
         <v>113.58</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -820,7 +823,7 @@
         <v>108.84</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -834,7 +837,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -848,7 +851,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -862,7 +865,7 @@
         <v>91.88</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -876,7 +879,7 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -890,7 +893,7 @@
         <v>137.52000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -904,7 +907,7 @@
         <v>102.52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -918,7 +921,7 @@
         <v>120.64</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -932,7 +935,7 @@
         <v>89.54</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -946,7 +949,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -960,7 +963,7 @@
         <v>101.82</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -974,7 +977,7 @@
         <v>112.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -988,7 +991,7 @@
         <v>133.18</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -1002,7 +1005,7 @@
         <v>99.12</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>82.72</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1030,7 +1033,7 @@
         <v>111.32</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -1044,7 +1047,7 @@
         <v>126.18</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1058,7 +1061,7 @@
         <v>101.46</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1072,7 +1075,7 @@
         <v>94.72</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1086,7 +1089,7 @@
         <v>98.74</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -1100,7 +1103,7 @@
         <v>118.88</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>150.12</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>129.96</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1142,7 +1145,7 @@
         <v>92.48</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1156,7 +1159,7 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -1170,7 +1173,7 @@
         <v>120.58</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -1184,7 +1187,7 @@
         <v>100.6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1198,7 +1201,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -1212,7 +1215,7 @@
         <v>139.82</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -1226,7 +1229,7 @@
         <v>102.56</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>92.98</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>16</v>
       </c>
@@ -1254,7 +1257,7 @@
         <v>102.22</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -1268,7 +1271,7 @@
         <v>153.08000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>34</v>
       </c>
@@ -1282,7 +1285,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>35</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>94.46</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1310,7 +1313,7 @@
         <v>108.38</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -1324,7 +1327,7 @@
         <v>97.34</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -1338,7 +1341,7 @@
         <v>97.38</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -1352,7 +1355,7 @@
         <v>125.02</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>96.72</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -1380,7 +1383,7 @@
         <v>118.06</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>99.64</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -1422,7 +1425,7 @@
         <v>82.84</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -1436,7 +1439,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -1450,7 +1453,7 @@
         <v>112.28</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>35</v>
       </c>
@@ -1464,7 +1467,7 @@
         <v>74.58</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -1478,7 +1481,7 @@
         <v>140.74</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -1492,7 +1495,7 @@
         <v>83.32</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>89.74</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -1520,7 +1523,7 @@
         <v>128.4</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -1534,7 +1537,7 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -1547,11 +1550,8 @@
       <c r="D74">
         <v>115.64</v>
       </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -1564,11 +1564,8 @@
       <c r="D75">
         <v>88.24</v>
       </c>
-      <c r="E75" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -1581,11 +1578,8 @@
       <c r="D76">
         <v>186.52</v>
       </c>
-      <c r="E76" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -1598,11 +1592,8 @@
       <c r="D77">
         <v>67.22</v>
       </c>
-      <c r="E77" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -1615,11 +1606,8 @@
       <c r="D78">
         <v>81.180000000000007</v>
       </c>
-      <c r="E78" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -1632,11 +1620,8 @@
       <c r="D79">
         <v>114.18</v>
       </c>
-      <c r="E79" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>35</v>
       </c>
@@ -1649,11 +1634,8 @@
       <c r="D80">
         <v>80.92</v>
       </c>
-      <c r="E80" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -1666,11 +1648,8 @@
       <c r="D81">
         <v>68.959999999999994</v>
       </c>
-      <c r="E81" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>19</v>
       </c>
@@ -1683,11 +1662,8 @@
       <c r="D82">
         <v>166.86</v>
       </c>
-      <c r="E82" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -1700,11 +1676,8 @@
       <c r="D83">
         <v>131.74</v>
       </c>
-      <c r="E83" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -1717,11 +1690,8 @@
       <c r="D84">
         <v>83.3</v>
       </c>
-      <c r="E84" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -1734,292 +1704,493 @@
       <c r="D85">
         <v>71.540000000000006</v>
       </c>
-      <c r="E85" t="s">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86">
+        <v>71.52</v>
+      </c>
+      <c r="D86">
+        <v>113.58</v>
+      </c>
+      <c r="E86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87">
+        <v>105.08</v>
+      </c>
+      <c r="D87">
+        <v>112.78</v>
+      </c>
+      <c r="E87" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>36</v>
+      </c>
+      <c r="C88">
+        <v>145.26</v>
+      </c>
+      <c r="D88">
+        <v>127.58</v>
+      </c>
+      <c r="E88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>16</v>
+      </c>
+      <c r="B89" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89">
+        <v>112.78</v>
+      </c>
+      <c r="D89">
+        <v>105.08</v>
+      </c>
+      <c r="E89" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90">
+        <v>132.46</v>
+      </c>
+      <c r="D90">
+        <v>100.32</v>
+      </c>
+      <c r="E90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>34</v>
+      </c>
+      <c r="B91" t="s">
+        <v>36</v>
+      </c>
+      <c r="C91">
+        <v>113.58</v>
+      </c>
+      <c r="D91">
+        <v>71.52</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>35</v>
+      </c>
+      <c r="B92" t="s">
+        <v>36</v>
+      </c>
+      <c r="C92">
+        <v>100.32</v>
+      </c>
+      <c r="D92">
+        <v>132.46</v>
+      </c>
+      <c r="E92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>18</v>
+      </c>
+      <c r="B93" t="s">
+        <v>36</v>
+      </c>
+      <c r="C93">
+        <v>86.46</v>
+      </c>
+      <c r="D93">
+        <v>81.28</v>
+      </c>
+      <c r="E93" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>36</v>
+      </c>
+      <c r="C94">
+        <v>129.18</v>
+      </c>
+      <c r="D94">
+        <v>94.2</v>
+      </c>
+      <c r="E94" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>20</v>
+      </c>
+      <c r="B95" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95">
+        <v>127.58</v>
+      </c>
+      <c r="D95">
+        <v>145.26</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96">
+        <v>81.28</v>
+      </c>
+      <c r="D96">
+        <v>86.46</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" t="s">
+        <v>36</v>
+      </c>
+      <c r="C97">
+        <v>94.2</v>
+      </c>
+      <c r="D97">
+        <v>129.18</v>
+      </c>
+      <c r="E97" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D98" s="1"/>
     </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D99" s="1"/>
     </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D100" s="1"/>
     </row>
-    <row r="103" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
     </row>
-    <row r="104" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C104" s="1"/>
     </row>
-    <row r="105" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D105" s="1"/>
     </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
     </row>
-    <row r="107" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
     </row>
-    <row r="108" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
     </row>
-    <row r="109" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
     </row>
-    <row r="110" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
     </row>
-    <row r="112" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
     </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
     </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
     </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
     </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
     </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
     </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
     </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
     </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
     </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
     </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
     </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
     </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
     </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
     </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
     </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
     </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
     </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
     </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
     </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
     </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
     </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
     </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
     </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
     </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
     </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
     </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
     </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
     </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
     </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
     </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
     </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
     </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
     </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
     </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
     </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
     </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
     </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
     </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
     </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
     </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
     </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
     </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
     </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
     </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{657FD601-2028-0A4F-BA12-553C96356FC4}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E73">
+    <sortState ref="A2:E73">
       <sortCondition ref="B1:B73"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C90:C101">
+  <sortState ref="C90:C101">
     <sortCondition ref="C90:C101"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/FFL_Data.xlsx
+++ b/FFL_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edenaxelrad/Desktop/FFL-Dash-2025-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axelrade\Downloads\FFL-Dash-2025-main (1)\FFL-Dash-2025-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BB9905-3458-BE45-876F-2C6BC6C65651}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35BC891-1086-4749-A707-775E2EF1A843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
+    <workbookView xWindow="-38520" yWindow="-1965" windowWidth="38640" windowHeight="21120" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 Results" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="38">
   <si>
     <t>Points Against</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>Week 8</t>
+  </si>
+  <si>
+    <t>Week 9</t>
   </si>
 </sst>
 </file>
@@ -207,9 +210,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -247,7 +250,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -353,7 +356,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -495,7 +498,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -504,15 +507,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657FD601-2028-0A4F-BA12-553C96356FC4}">
   <dimension ref="A1:E169"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -529,7 +532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -543,7 +546,7 @@
         <v>124.56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -557,7 +560,7 @@
         <v>76.12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -571,7 +574,7 @@
         <v>108.82</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -585,7 +588,7 @@
         <v>101.22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -599,7 +602,7 @@
         <v>56.94</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -613,7 +616,7 @@
         <v>122.52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -627,7 +630,7 @@
         <v>101.88</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -641,7 +644,7 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -655,7 +658,7 @@
         <v>120.96</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -669,7 +672,7 @@
         <v>93.52</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -683,7 +686,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -697,7 +700,7 @@
         <v>99.48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -711,7 +714,7 @@
         <v>93.72</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -725,7 +728,7 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -739,7 +742,7 @@
         <v>128.44</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -753,7 +756,7 @@
         <v>109.18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -767,7 +770,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -781,7 +784,7 @@
         <v>92.18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -795,7 +798,7 @@
         <v>99.82</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -809,7 +812,7 @@
         <v>113.58</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -823,7 +826,7 @@
         <v>108.84</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -837,7 +840,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -851,7 +854,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -865,7 +868,7 @@
         <v>91.88</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -879,7 +882,7 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -893,7 +896,7 @@
         <v>137.52000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -907,7 +910,7 @@
         <v>102.52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -921,7 +924,7 @@
         <v>120.64</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -935,7 +938,7 @@
         <v>89.54</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -949,7 +952,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -963,7 +966,7 @@
         <v>101.82</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -977,7 +980,7 @@
         <v>112.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -991,7 +994,7 @@
         <v>133.18</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -1005,7 +1008,7 @@
         <v>99.12</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1019,7 +1022,7 @@
         <v>82.72</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>111.32</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -1047,7 +1050,7 @@
         <v>126.18</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1061,7 +1064,7 @@
         <v>101.46</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>94.72</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>98.74</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>118.88</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1117,7 +1120,7 @@
         <v>150.12</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>129.96</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1145,7 +1148,7 @@
         <v>92.48</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1159,7 +1162,7 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -1173,7 +1176,7 @@
         <v>120.58</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>100.6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1201,7 +1204,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -1215,7 +1218,7 @@
         <v>139.82</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -1229,7 +1232,7 @@
         <v>102.56</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -1243,7 +1246,7 @@
         <v>92.98</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>16</v>
       </c>
@@ -1257,7 +1260,7 @@
         <v>102.22</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -1271,7 +1274,7 @@
         <v>153.08000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>34</v>
       </c>
@@ -1285,7 +1288,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>35</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>94.46</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1313,7 +1316,7 @@
         <v>108.38</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -1327,7 +1330,7 @@
         <v>97.34</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -1341,7 +1344,7 @@
         <v>97.38</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>125.02</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -1369,7 +1372,7 @@
         <v>96.72</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -1383,7 +1386,7 @@
         <v>118.06</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -1397,7 +1400,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -1411,7 +1414,7 @@
         <v>99.64</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -1425,7 +1428,7 @@
         <v>82.84</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -1439,7 +1442,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>112.28</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>35</v>
       </c>
@@ -1467,7 +1470,7 @@
         <v>74.58</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -1481,7 +1484,7 @@
         <v>140.74</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>83.32</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -1509,7 +1512,7 @@
         <v>89.74</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -1523,7 +1526,7 @@
         <v>128.4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -1537,7 +1540,7 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -1551,7 +1554,7 @@
         <v>115.64</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>88.24</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -1579,7 +1582,7 @@
         <v>186.52</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -1593,7 +1596,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -1607,7 +1610,7 @@
         <v>81.180000000000007</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -1621,7 +1624,7 @@
         <v>114.18</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>35</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>80.92</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -1649,7 +1652,7 @@
         <v>68.959999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>19</v>
       </c>
@@ -1663,7 +1666,7 @@
         <v>166.86</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -1677,7 +1680,7 @@
         <v>131.74</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -1691,7 +1694,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -1705,7 +1708,7 @@
         <v>71.540000000000006</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -1718,11 +1721,8 @@
       <c r="D86">
         <v>113.58</v>
       </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -1735,11 +1735,8 @@
       <c r="D87">
         <v>112.78</v>
       </c>
-      <c r="E87" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -1752,11 +1749,8 @@
       <c r="D88">
         <v>127.58</v>
       </c>
-      <c r="E88" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -1769,11 +1763,8 @@
       <c r="D89">
         <v>105.08</v>
       </c>
-      <c r="E89" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -1786,11 +1777,8 @@
       <c r="D90">
         <v>100.32</v>
       </c>
-      <c r="E90" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>34</v>
       </c>
@@ -1803,11 +1791,8 @@
       <c r="D91">
         <v>71.52</v>
       </c>
-      <c r="E91" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>35</v>
       </c>
@@ -1820,11 +1805,8 @@
       <c r="D92">
         <v>132.46</v>
       </c>
-      <c r="E92" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -1837,11 +1819,8 @@
       <c r="D93">
         <v>81.28</v>
       </c>
-      <c r="E93" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -1854,11 +1833,8 @@
       <c r="D94">
         <v>94.2</v>
       </c>
-      <c r="E94" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>20</v>
       </c>
@@ -1871,11 +1847,8 @@
       <c r="D95">
         <v>145.26</v>
       </c>
-      <c r="E95" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -1888,11 +1861,8 @@
       <c r="D96">
         <v>86.46</v>
       </c>
-      <c r="E96" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -1905,292 +1875,458 @@
       <c r="D97">
         <v>129.18</v>
       </c>
-      <c r="E97" t="s">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98">
+        <v>152.4</v>
+      </c>
+      <c r="D98" s="1">
+        <v>94.66</v>
+      </c>
+      <c r="E98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B99" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99">
+        <v>111.66</v>
+      </c>
+      <c r="D99" s="1">
+        <v>113.24</v>
+      </c>
+      <c r="E99" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100">
+        <v>95.7</v>
+      </c>
+      <c r="D100" s="1">
+        <v>124.92</v>
+      </c>
+      <c r="E100" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>16</v>
+      </c>
+      <c r="B101" t="s">
+        <v>37</v>
+      </c>
+      <c r="C101">
+        <v>102.8</v>
+      </c>
+      <c r="D101" s="1">
+        <v>120.22</v>
+      </c>
+      <c r="E101" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B102" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" s="1">
+        <v>124.92</v>
+      </c>
+      <c r="D102">
+        <v>95.7</v>
+      </c>
+      <c r="E102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>34</v>
+      </c>
+      <c r="B103" t="s">
+        <v>37</v>
+      </c>
+      <c r="C103" s="1">
+        <v>71.64</v>
+      </c>
+      <c r="D103" s="1">
+        <v>136.72</v>
+      </c>
+      <c r="E103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>35</v>
+      </c>
+      <c r="B104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" s="1">
+        <v>119.6</v>
+      </c>
+      <c r="D104" s="1">
+        <v>125.9</v>
+      </c>
+      <c r="E104" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>18</v>
+      </c>
+      <c r="B105" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="1">
+        <v>113.24</v>
+      </c>
+      <c r="D105">
+        <v>111.66</v>
+      </c>
+      <c r="E105" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>19</v>
+      </c>
+      <c r="B106" t="s">
+        <v>37</v>
+      </c>
+      <c r="C106" s="1">
+        <v>94.66</v>
+      </c>
+      <c r="D106">
+        <v>152.4</v>
+      </c>
+      <c r="E106" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>20</v>
+      </c>
+      <c r="B107" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107" s="1">
+        <v>120.22</v>
+      </c>
+      <c r="D107">
+        <v>102.8</v>
+      </c>
+      <c r="E107" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C108" s="1">
+        <v>136.72</v>
+      </c>
+      <c r="D108" s="1">
+        <v>71.64</v>
+      </c>
+      <c r="E108" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>37</v>
+      </c>
+      <c r="C109" s="1">
+        <v>125.9</v>
+      </c>
+      <c r="D109" s="1">
+        <v>119.6</v>
+      </c>
+      <c r="E109" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D98" s="1"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D99" s="1"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D100" s="1"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C104" s="1"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D105" s="1"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
     </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
     </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
     </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
     </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
     </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
     </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
     </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
     </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
     </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
     </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
     </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
     </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
     </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
     </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
     </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
     </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
     </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
     </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
     </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
     </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
     </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
     </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
     </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
     </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
     </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
     </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
     </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
     </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
     </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
     </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
     </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
     </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
     </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
     </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
     </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
     </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
     </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
     </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
     </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
     </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
     </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
     </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
     </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
     </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{657FD601-2028-0A4F-BA12-553C96356FC4}">
-    <sortState ref="A2:E73">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E73">
       <sortCondition ref="B1:B73"/>
     </sortState>
   </autoFilter>
-  <sortState ref="C90:C101">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C90:C101">
     <sortCondition ref="C90:C101"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/FFL_Data.xlsx
+++ b/FFL_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axelrade\Downloads\FFL-Dash-2025-main (1)\FFL-Dash-2025-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axelrade\Downloads\FFL-Dash-2025-main\FFL-Dash-2025-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35BC891-1086-4749-A707-775E2EF1A843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E923DF0-8197-46EC-9094-FBE431A16594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1965" windowWidth="38640" windowHeight="21120" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 Results" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="39">
   <si>
     <t>Points Against</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>Week 9</t>
+  </si>
+  <si>
+    <t>Week 10</t>
   </si>
 </sst>
 </file>
@@ -507,15 +510,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657FD601-2028-0A4F-BA12-553C96356FC4}">
   <dimension ref="A1:E169"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="33.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -532,7 +535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -546,7 +549,7 @@
         <v>124.56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -560,7 +563,7 @@
         <v>76.12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -574,7 +577,7 @@
         <v>108.82</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -588,7 +591,7 @@
         <v>101.22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -602,7 +605,7 @@
         <v>56.94</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -616,7 +619,7 @@
         <v>122.52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -630,7 +633,7 @@
         <v>101.88</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -644,7 +647,7 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -658,7 +661,7 @@
         <v>120.96</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -672,7 +675,7 @@
         <v>93.52</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -686,7 +689,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -700,7 +703,7 @@
         <v>99.48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -714,7 +717,7 @@
         <v>93.72</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -728,7 +731,7 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -742,7 +745,7 @@
         <v>128.44</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -756,7 +759,7 @@
         <v>109.18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -770,7 +773,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -784,7 +787,7 @@
         <v>92.18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -798,7 +801,7 @@
         <v>99.82</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -812,7 +815,7 @@
         <v>113.58</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -826,7 +829,7 @@
         <v>108.84</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -840,7 +843,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -854,7 +857,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -868,7 +871,7 @@
         <v>91.88</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -882,7 +885,7 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -896,7 +899,7 @@
         <v>137.52000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -910,7 +913,7 @@
         <v>102.52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -924,7 +927,7 @@
         <v>120.64</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -938,7 +941,7 @@
         <v>89.54</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -952,7 +955,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -966,7 +969,7 @@
         <v>101.82</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -980,7 +983,7 @@
         <v>112.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -994,7 +997,7 @@
         <v>133.18</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -1008,7 +1011,7 @@
         <v>99.12</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1022,7 +1025,7 @@
         <v>82.72</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1036,7 +1039,7 @@
         <v>111.32</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -1050,7 +1053,7 @@
         <v>126.18</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>101.46</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1078,7 +1081,7 @@
         <v>94.72</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1092,7 +1095,7 @@
         <v>98.74</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -1106,7 +1109,7 @@
         <v>118.88</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>150.12</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1134,7 +1137,7 @@
         <v>129.96</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>92.48</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1162,7 +1165,7 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>120.58</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -1190,7 +1193,7 @@
         <v>100.6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1204,7 +1207,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -1218,7 +1221,7 @@
         <v>139.82</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>102.56</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -1246,7 +1249,7 @@
         <v>92.98</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>16</v>
       </c>
@@ -1260,7 +1263,7 @@
         <v>102.22</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -1274,7 +1277,7 @@
         <v>153.08000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>34</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>35</v>
       </c>
@@ -1302,7 +1305,7 @@
         <v>94.46</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1316,7 +1319,7 @@
         <v>108.38</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -1330,7 +1333,7 @@
         <v>97.34</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -1344,7 +1347,7 @@
         <v>97.38</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -1358,7 +1361,7 @@
         <v>125.02</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -1372,7 +1375,7 @@
         <v>96.72</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>118.06</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -1400,7 +1403,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>99.64</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -1428,7 +1431,7 @@
         <v>82.84</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -1442,7 +1445,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -1456,7 +1459,7 @@
         <v>112.28</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>35</v>
       </c>
@@ -1470,7 +1473,7 @@
         <v>74.58</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>140.74</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -1498,7 +1501,7 @@
         <v>83.32</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -1512,7 +1515,7 @@
         <v>89.74</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -1526,7 +1529,7 @@
         <v>128.4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -1540,7 +1543,7 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>115.64</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -1568,7 +1571,7 @@
         <v>88.24</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -1582,7 +1585,7 @@
         <v>186.52</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -1610,7 +1613,7 @@
         <v>81.180000000000007</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -1624,7 +1627,7 @@
         <v>114.18</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>35</v>
       </c>
@@ -1638,7 +1641,7 @@
         <v>80.92</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -1652,7 +1655,7 @@
         <v>68.959999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>19</v>
       </c>
@@ -1666,7 +1669,7 @@
         <v>166.86</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -1680,7 +1683,7 @@
         <v>131.74</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -1694,7 +1697,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -1708,7 +1711,7 @@
         <v>71.540000000000006</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -1722,7 +1725,7 @@
         <v>113.58</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -1736,7 +1739,7 @@
         <v>112.78</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>127.58</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -1764,7 +1767,7 @@
         <v>105.08</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>100.32</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>34</v>
       </c>
@@ -1792,7 +1795,7 @@
         <v>71.52</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>35</v>
       </c>
@@ -1806,7 +1809,7 @@
         <v>132.46</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -1820,7 +1823,7 @@
         <v>81.28</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -1834,7 +1837,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>20</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>145.26</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -1862,7 +1865,7 @@
         <v>86.46</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -1876,7 +1879,7 @@
         <v>129.18</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>9</v>
       </c>
@@ -1889,11 +1892,8 @@
       <c r="D98" s="1">
         <v>94.66</v>
       </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>14</v>
       </c>
@@ -1906,11 +1906,8 @@
       <c r="D99" s="1">
         <v>113.24</v>
       </c>
-      <c r="E99" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>15</v>
       </c>
@@ -1923,11 +1920,8 @@
       <c r="D100" s="1">
         <v>124.92</v>
       </c>
-      <c r="E100" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -1940,11 +1934,8 @@
       <c r="D101" s="1">
         <v>120.22</v>
       </c>
-      <c r="E101" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -1957,11 +1948,8 @@
       <c r="D102">
         <v>95.7</v>
       </c>
-      <c r="E102" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>34</v>
       </c>
@@ -1974,11 +1962,8 @@
       <c r="D103" s="1">
         <v>136.72</v>
       </c>
-      <c r="E103" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -1991,11 +1976,8 @@
       <c r="D104" s="1">
         <v>125.9</v>
       </c>
-      <c r="E104" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -2008,11 +1990,8 @@
       <c r="D105">
         <v>111.66</v>
       </c>
-      <c r="E105" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -2025,11 +2004,8 @@
       <c r="D106">
         <v>152.4</v>
       </c>
-      <c r="E106" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>20</v>
       </c>
@@ -2042,11 +2018,8 @@
       <c r="D107">
         <v>102.8</v>
       </c>
-      <c r="E107" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>12</v>
       </c>
@@ -2059,11 +2032,8 @@
       <c r="D108" s="1">
         <v>71.64</v>
       </c>
-      <c r="E108" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -2076,247 +2046,400 @@
       <c r="D109" s="1">
         <v>119.6</v>
       </c>
-      <c r="E109" t="s">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>38</v>
+      </c>
+      <c r="C110" s="1">
+        <v>90.84</v>
+      </c>
+      <c r="D110" s="1">
+        <v>146.19999999999999</v>
+      </c>
+      <c r="E110" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" t="s">
+        <v>38</v>
+      </c>
+      <c r="C111" s="1">
+        <v>153.94</v>
+      </c>
+      <c r="D111" s="1">
+        <v>112.3</v>
+      </c>
+      <c r="E111" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>38</v>
+      </c>
+      <c r="C112" s="1">
+        <v>85.68</v>
+      </c>
+      <c r="D112" s="1">
+        <v>110.62</v>
+      </c>
+      <c r="E112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>16</v>
+      </c>
+      <c r="B113" t="s">
+        <v>38</v>
+      </c>
+      <c r="C113" s="1">
+        <v>94.4</v>
+      </c>
+      <c r="D113" s="1">
+        <v>95.7</v>
+      </c>
+      <c r="E113" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>17</v>
+      </c>
+      <c r="B114" t="s">
+        <v>38</v>
+      </c>
+      <c r="C114" s="1">
+        <v>95.7</v>
+      </c>
+      <c r="D114" s="1">
+        <v>94.4</v>
+      </c>
+      <c r="E114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>34</v>
+      </c>
+      <c r="B115" t="s">
+        <v>38</v>
+      </c>
+      <c r="C115" s="1">
+        <v>112.3</v>
+      </c>
+      <c r="D115" s="1">
+        <v>153.94</v>
+      </c>
+      <c r="E115" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>35</v>
+      </c>
+      <c r="B116" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="1">
+        <v>110.62</v>
+      </c>
+      <c r="D116" s="1">
+        <v>85.68</v>
+      </c>
+      <c r="E116" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>18</v>
+      </c>
+      <c r="B117" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="1">
+        <v>128.82</v>
+      </c>
+      <c r="D117" s="1">
+        <v>127.64</v>
+      </c>
+      <c r="E117" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" t="s">
+        <v>38</v>
+      </c>
+      <c r="C118" s="1">
+        <v>106.2</v>
+      </c>
+      <c r="D118" s="1">
+        <v>92.02</v>
+      </c>
+      <c r="E118" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>20</v>
+      </c>
+      <c r="B119" t="s">
+        <v>38</v>
+      </c>
+      <c r="C119" s="1">
+        <v>127.64</v>
+      </c>
+      <c r="D119" s="1">
+        <v>128.82</v>
+      </c>
+      <c r="E119" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>12</v>
+      </c>
+      <c r="B120" t="s">
+        <v>38</v>
+      </c>
+      <c r="C120" s="1">
+        <v>92.02</v>
+      </c>
+      <c r="D120" s="1">
+        <v>106.2</v>
+      </c>
+      <c r="E120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" t="s">
+        <v>38</v>
+      </c>
+      <c r="C121" s="1">
+        <v>146.19999999999999</v>
+      </c>
+      <c r="D121" s="1">
+        <v>90.84</v>
+      </c>
+      <c r="E121" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-    </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-    </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-    </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-    </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-    </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-    </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-    </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-    </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-    </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-    </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
     </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
     </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
     </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
     </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
     </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
     </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
     </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
     </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
     </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
     </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
     </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
     </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
     </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
     </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
     </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
     </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
     </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
     </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
     </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
     </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
     </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
     </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
     </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
     </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
     </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
     </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
     </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
     </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
     </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
     </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
     </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
     </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
     </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
     </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
     </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
     </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
     </row>

--- a/FFL_Data.xlsx
+++ b/FFL_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axelrade\Downloads\FFL-Dash-2025-main\FFL-Dash-2025-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E923DF0-8197-46EC-9094-FBE431A16594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9E75DA-F3A0-46E1-AAD3-7BC590BBF0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 Results" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="42">
   <si>
     <t>Points Against</t>
   </si>
@@ -78,9 +78,6 @@
     <t>CoHo Chicken Tet</t>
   </si>
   <si>
-    <t>Stone (injured) Kittles</t>
-  </si>
-  <si>
     <t>The Legend of Drewkeys</t>
   </si>
   <si>
@@ -145,6 +142,18 @@
   </si>
   <si>
     <t>Week 10</t>
+  </si>
+  <si>
+    <t>Week 11</t>
+  </si>
+  <si>
+    <t>Week 12</t>
+  </si>
+  <si>
+    <t>Week 13</t>
+  </si>
+  <si>
+    <t>Stone Cold Kittles</t>
   </si>
 </sst>
 </file>
@@ -510,15 +519,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657FD601-2028-0A4F-BA12-553C96356FC4}">
   <dimension ref="A1:E169"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1796875" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -535,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -549,7 +558,7 @@
         <v>124.56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -563,7 +572,7 @@
         <v>76.12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -577,9 +586,9 @@
         <v>108.82</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -591,9 +600,9 @@
         <v>101.22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -605,9 +614,9 @@
         <v>56.94</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -619,9 +628,9 @@
         <v>122.52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -633,9 +642,9 @@
         <v>101.88</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -647,9 +656,9 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -661,9 +670,9 @@
         <v>120.96</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -675,7 +684,7 @@
         <v>93.52</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -689,7 +698,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -703,7 +712,7 @@
         <v>99.48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -717,7 +726,7 @@
         <v>93.72</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -731,7 +740,7 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -745,9 +754,9 @@
         <v>128.44</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -759,9 +768,9 @@
         <v>109.18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -773,9 +782,9 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -787,9 +796,9 @@
         <v>92.18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -801,9 +810,9 @@
         <v>99.82</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -815,9 +824,9 @@
         <v>113.58</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -829,9 +838,9 @@
         <v>108.84</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -843,7 +852,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -857,7 +866,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -871,7 +880,7 @@
         <v>91.88</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -885,7 +894,7 @@
         <v>87.38</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -899,7 +908,7 @@
         <v>137.52000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -913,9 +922,9 @@
         <v>102.52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -927,9 +936,9 @@
         <v>120.64</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
@@ -941,9 +950,9 @@
         <v>89.54</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
@@ -955,9 +964,9 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
@@ -969,9 +978,9 @@
         <v>101.82</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
@@ -983,9 +992,9 @@
         <v>112.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
@@ -997,9 +1006,9 @@
         <v>133.18</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -1011,7 +1020,7 @@
         <v>99.12</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1025,7 +1034,7 @@
         <v>82.72</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1039,12 +1048,12 @@
         <v>111.32</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38">
         <v>129.96</v>
@@ -1053,12 +1062,12 @@
         <v>126.18</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C39">
         <v>120.58</v>
@@ -1067,12 +1076,12 @@
         <v>101.46</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40">
         <v>93.3</v>
@@ -1081,12 +1090,12 @@
         <v>94.72</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41">
         <v>150.12</v>
@@ -1095,12 +1104,12 @@
         <v>98.74</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C42">
         <v>100.6</v>
@@ -1109,12 +1118,12 @@
         <v>118.88</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C43">
         <v>98.74</v>
@@ -1123,12 +1132,12 @@
         <v>150.12</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>126.18</v>
@@ -1137,12 +1146,12 @@
         <v>129.96</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C45">
         <v>165</v>
@@ -1151,12 +1160,12 @@
         <v>92.48</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46">
         <v>94.72</v>
@@ -1165,12 +1174,12 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47">
         <v>101.46</v>
@@ -1179,12 +1188,12 @@
         <v>120.58</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C48">
         <v>118.88</v>
@@ -1193,12 +1202,12 @@
         <v>100.6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C49">
         <v>92.48</v>
@@ -1207,12 +1216,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C50">
         <v>92.98</v>
@@ -1221,12 +1230,12 @@
         <v>139.82</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C51">
         <v>153.08000000000001</v>
@@ -1235,12 +1244,12 @@
         <v>102.56</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C52">
         <v>139.82</v>
@@ -1249,12 +1258,12 @@
         <v>92.98</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C53">
         <v>97.34</v>
@@ -1263,12 +1272,12 @@
         <v>102.22</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C54">
         <v>102.56</v>
@@ -1277,12 +1286,12 @@
         <v>153.08000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55">
         <v>108.38</v>
@@ -1291,12 +1300,12 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C56">
         <v>125.02</v>
@@ -1305,12 +1314,12 @@
         <v>94.46</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C57">
         <v>109.5</v>
@@ -1319,12 +1328,12 @@
         <v>108.38</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58">
         <v>102.22</v>
@@ -1333,12 +1342,12 @@
         <v>97.34</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59">
         <v>96.72</v>
@@ -1347,12 +1356,12 @@
         <v>97.38</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C60">
         <v>94.46</v>
@@ -1361,12 +1370,12 @@
         <v>125.02</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C61">
         <v>97.38</v>
@@ -1375,12 +1384,12 @@
         <v>96.72</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C62">
         <v>82.84</v>
@@ -1389,12 +1398,12 @@
         <v>118.06</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C63">
         <v>74.58</v>
@@ -1403,12 +1412,12 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C64">
         <v>128.4</v>
@@ -1417,12 +1426,12 @@
         <v>99.64</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65">
         <v>118.06</v>
@@ -1431,12 +1440,12 @@
         <v>82.84</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C66">
         <v>89.74</v>
@@ -1445,12 +1454,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C67">
         <v>104.76</v>
@@ -1459,12 +1468,12 @@
         <v>112.28</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68">
         <v>63.1</v>
@@ -1473,12 +1482,12 @@
         <v>74.58</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C69">
         <v>83.32</v>
@@ -1487,12 +1496,12 @@
         <v>140.74</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C70">
         <v>140.74</v>
@@ -1501,12 +1510,12 @@
         <v>83.32</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C71">
         <v>105</v>
@@ -1515,12 +1524,12 @@
         <v>89.74</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C72">
         <v>99.64</v>
@@ -1529,12 +1538,12 @@
         <v>128.4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C73">
         <v>112.28</v>
@@ -1543,12 +1552,12 @@
         <v>104.76</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C74">
         <v>68.959999999999994</v>
@@ -1557,12 +1566,12 @@
         <v>115.64</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C75">
         <v>186.52</v>
@@ -1571,12 +1580,12 @@
         <v>88.24</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C76">
         <v>88.24</v>
@@ -1585,12 +1594,12 @@
         <v>186.52</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C77">
         <v>83.3</v>
@@ -1599,12 +1608,12 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C78">
         <v>71.540000000000006</v>
@@ -1613,12 +1622,12 @@
         <v>81.180000000000007</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C79">
         <v>166.86</v>
@@ -1627,12 +1636,12 @@
         <v>114.18</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C80">
         <v>131.74</v>
@@ -1641,12 +1650,12 @@
         <v>80.92</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C81">
         <v>115.64</v>
@@ -1655,12 +1664,12 @@
         <v>68.959999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C82">
         <v>114.18</v>
@@ -1669,12 +1678,12 @@
         <v>166.86</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C83">
         <v>80.92</v>
@@ -1683,12 +1692,12 @@
         <v>131.74</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C84">
         <v>67.22</v>
@@ -1697,12 +1706,12 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C85">
         <v>81.180000000000007</v>
@@ -1711,12 +1720,12 @@
         <v>71.540000000000006</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C86">
         <v>71.52</v>
@@ -1725,12 +1734,12 @@
         <v>113.58</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87">
         <v>105.08</v>
@@ -1739,12 +1748,12 @@
         <v>112.78</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C88">
         <v>145.26</v>
@@ -1753,12 +1762,12 @@
         <v>127.58</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C89">
         <v>112.78</v>
@@ -1767,12 +1776,12 @@
         <v>105.08</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B90" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C90">
         <v>132.46</v>
@@ -1781,12 +1790,12 @@
         <v>100.32</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C91">
         <v>113.58</v>
@@ -1795,12 +1804,12 @@
         <v>71.52</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>34</v>
+      </c>
+      <c r="B92" t="s">
         <v>35</v>
-      </c>
-      <c r="B92" t="s">
-        <v>36</v>
       </c>
       <c r="C92">
         <v>100.32</v>
@@ -1809,12 +1818,12 @@
         <v>132.46</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C93">
         <v>86.46</v>
@@ -1823,12 +1832,12 @@
         <v>81.28</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C94">
         <v>129.18</v>
@@ -1837,12 +1846,12 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C95">
         <v>127.58</v>
@@ -1851,12 +1860,12 @@
         <v>145.26</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C96">
         <v>81.28</v>
@@ -1865,12 +1874,12 @@
         <v>86.46</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C97">
         <v>94.2</v>
@@ -1879,12 +1888,12 @@
         <v>129.18</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C98">
         <v>152.4</v>
@@ -1893,12 +1902,12 @@
         <v>94.66</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C99">
         <v>111.66</v>
@@ -1907,12 +1916,12 @@
         <v>113.24</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C100">
         <v>95.7</v>
@@ -1921,12 +1930,12 @@
         <v>124.92</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C101">
         <v>102.8</v>
@@ -1935,12 +1944,12 @@
         <v>120.22</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C102" s="1">
         <v>124.92</v>
@@ -1949,12 +1958,12 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C103" s="1">
         <v>71.64</v>
@@ -1963,12 +1972,12 @@
         <v>136.72</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1">
         <v>119.6</v>
@@ -1977,12 +1986,12 @@
         <v>125.9</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C105" s="1">
         <v>113.24</v>
@@ -1991,12 +2000,12 @@
         <v>111.66</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C106" s="1">
         <v>94.66</v>
@@ -2005,12 +2014,12 @@
         <v>152.4</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C107" s="1">
         <v>120.22</v>
@@ -2019,12 +2028,12 @@
         <v>102.8</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C108" s="1">
         <v>136.72</v>
@@ -2033,12 +2042,12 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C109" s="1">
         <v>125.9</v>
@@ -2047,12 +2056,12 @@
         <v>119.6</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C110" s="1">
         <v>90.84</v>
@@ -2060,16 +2069,13 @@
       <c r="D110" s="1">
         <v>146.19999999999999</v>
       </c>
-      <c r="E110" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C111" s="1">
         <v>153.94</v>
@@ -2077,16 +2083,13 @@
       <c r="D111" s="1">
         <v>112.3</v>
       </c>
-      <c r="E111" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C112" s="1">
         <v>85.68</v>
@@ -2094,16 +2097,13 @@
       <c r="D112" s="1">
         <v>110.62</v>
       </c>
-      <c r="E112" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B113" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C113" s="1">
         <v>94.4</v>
@@ -2111,16 +2111,13 @@
       <c r="D113" s="1">
         <v>95.7</v>
       </c>
-      <c r="E113" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B114" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C114" s="1">
         <v>95.7</v>
@@ -2128,16 +2125,13 @@
       <c r="D114" s="1">
         <v>94.4</v>
       </c>
-      <c r="E114" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C115" s="1">
         <v>112.3</v>
@@ -2145,16 +2139,13 @@
       <c r="D115" s="1">
         <v>153.94</v>
       </c>
-      <c r="E115" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B116" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C116" s="1">
         <v>110.62</v>
@@ -2162,16 +2153,13 @@
       <c r="D116" s="1">
         <v>85.68</v>
       </c>
-      <c r="E116" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C117" s="1">
         <v>128.82</v>
@@ -2179,16 +2167,13 @@
       <c r="D117" s="1">
         <v>127.64</v>
       </c>
-      <c r="E117" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B118" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C118" s="1">
         <v>106.2</v>
@@ -2196,16 +2181,13 @@
       <c r="D118" s="1">
         <v>92.02</v>
       </c>
-      <c r="E118" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C119" s="1">
         <v>127.64</v>
@@ -2213,16 +2195,13 @@
       <c r="D119" s="1">
         <v>128.82</v>
       </c>
-      <c r="E119" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C120" s="1">
         <v>92.02</v>
@@ -2230,16 +2209,13 @@
       <c r="D120" s="1">
         <v>106.2</v>
       </c>
-      <c r="E120" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C121" s="1">
         <v>146.19999999999999</v>
@@ -2247,199 +2223,592 @@
       <c r="D121" s="1">
         <v>90.84</v>
       </c>
-      <c r="E121" t="s">
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>9</v>
+      </c>
+      <c r="B122" t="s">
+        <v>38</v>
+      </c>
+      <c r="C122" s="1">
+        <v>78.92</v>
+      </c>
+      <c r="D122" s="1">
+        <v>102.72</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" t="s">
+        <v>38</v>
+      </c>
+      <c r="C123" s="1">
+        <v>74.819999999999993</v>
+      </c>
+      <c r="D123" s="1">
+        <v>110.74</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>38</v>
+      </c>
+      <c r="C124" s="1">
+        <v>107.84</v>
+      </c>
+      <c r="D124" s="1">
+        <v>98.52</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>41</v>
+      </c>
+      <c r="B125" t="s">
+        <v>38</v>
+      </c>
+      <c r="C125" s="1">
+        <v>137.63999999999999</v>
+      </c>
+      <c r="D125" s="1">
+        <v>106.52</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>16</v>
+      </c>
+      <c r="B126" t="s">
+        <v>38</v>
+      </c>
+      <c r="C126" s="1">
+        <v>98.1</v>
+      </c>
+      <c r="D126" s="1">
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>33</v>
+      </c>
+      <c r="B127" t="s">
+        <v>38</v>
+      </c>
+      <c r="C127" s="1">
+        <v>92.52</v>
+      </c>
+      <c r="D127" s="1">
+        <v>90.08</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>34</v>
+      </c>
+      <c r="B128" t="s">
+        <v>38</v>
+      </c>
+      <c r="C128" s="1">
+        <v>106.52</v>
+      </c>
+      <c r="D128" s="1">
+        <v>137.63999999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>17</v>
+      </c>
+      <c r="B129" t="s">
+        <v>38</v>
+      </c>
+      <c r="C129" s="1">
+        <v>83.4</v>
+      </c>
+      <c r="D129" s="1">
+        <v>98.1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>18</v>
+      </c>
+      <c r="B130" t="s">
+        <v>38</v>
+      </c>
+      <c r="C130" s="1">
+        <v>110.74</v>
+      </c>
+      <c r="D130" s="1">
+        <v>74.819999999999993</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>19</v>
+      </c>
+      <c r="B131" t="s">
+        <v>38</v>
+      </c>
+      <c r="C131" s="1">
+        <v>90.08</v>
+      </c>
+      <c r="D131" s="1">
+        <v>92.52</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132" t="s">
+        <v>38</v>
+      </c>
+      <c r="C132" s="1">
+        <v>102.72</v>
+      </c>
+      <c r="D132" s="1">
+        <v>78.92</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" t="s">
+        <v>38</v>
+      </c>
+      <c r="C133" s="1">
+        <v>98.52</v>
+      </c>
+      <c r="D133" s="1">
+        <v>107.84</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134" t="s">
+        <v>39</v>
+      </c>
+      <c r="C134" s="1">
+        <v>110.16</v>
+      </c>
+      <c r="D134" s="1">
+        <v>100.12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>14</v>
+      </c>
+      <c r="B135" t="s">
+        <v>39</v>
+      </c>
+      <c r="C135" s="1">
+        <v>100.12</v>
+      </c>
+      <c r="D135" s="1">
+        <v>110.16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>39</v>
+      </c>
+      <c r="C136" s="1">
+        <v>117.58</v>
+      </c>
+      <c r="D136" s="1">
+        <v>117.66</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>41</v>
+      </c>
+      <c r="B137" t="s">
+        <v>39</v>
+      </c>
+      <c r="C137" s="1">
+        <v>117.66</v>
+      </c>
+      <c r="D137" s="1">
+        <v>117.58</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>16</v>
+      </c>
+      <c r="B138" t="s">
+        <v>39</v>
+      </c>
+      <c r="C138" s="1">
+        <v>101.72</v>
+      </c>
+      <c r="D138" s="1">
+        <v>132.76</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>33</v>
+      </c>
+      <c r="B139" t="s">
+        <v>39</v>
+      </c>
+      <c r="C139" s="1">
+        <v>132.76</v>
+      </c>
+      <c r="D139" s="1">
+        <v>101.72</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>34</v>
+      </c>
+      <c r="B140" t="s">
+        <v>39</v>
+      </c>
+      <c r="C140" s="1">
+        <v>119.18</v>
+      </c>
+      <c r="D140" s="1">
+        <v>125.76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>17</v>
+      </c>
+      <c r="B141" t="s">
+        <v>39</v>
+      </c>
+      <c r="C141" s="1">
+        <v>125.76</v>
+      </c>
+      <c r="D141" s="1">
+        <v>119.18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>18</v>
+      </c>
+      <c r="B142" t="s">
+        <v>39</v>
+      </c>
+      <c r="C142" s="1">
+        <v>87.06</v>
+      </c>
+      <c r="D142" s="1">
+        <v>84.52</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143" t="s">
+        <v>39</v>
+      </c>
+      <c r="C143" s="1">
+        <v>84.52</v>
+      </c>
+      <c r="D143" s="1">
+        <v>87.06</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>12</v>
+      </c>
+      <c r="B144" t="s">
+        <v>39</v>
+      </c>
+      <c r="C144" s="1">
+        <v>72.540000000000006</v>
+      </c>
+      <c r="D144" s="1">
+        <v>156.76</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" t="s">
+        <v>39</v>
+      </c>
+      <c r="C145" s="1">
+        <v>156.76</v>
+      </c>
+      <c r="D145" s="1">
+        <v>72.540000000000006</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" t="s">
+        <v>40</v>
+      </c>
+      <c r="C146" s="1">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="D146" s="1">
+        <v>97.62</v>
+      </c>
+      <c r="E146" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>14</v>
+      </c>
+      <c r="B147" t="s">
+        <v>40</v>
+      </c>
+      <c r="C147" s="1">
+        <v>98.24</v>
+      </c>
+      <c r="D147" s="1">
+        <v>144.56</v>
+      </c>
+      <c r="E147" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>40</v>
+      </c>
+      <c r="C148" s="1">
+        <v>113.94</v>
+      </c>
+      <c r="D148" s="1">
+        <v>122.4</v>
+      </c>
+      <c r="E148" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" t="s">
+        <v>40</v>
+      </c>
+      <c r="C149" s="1">
+        <v>84.54</v>
+      </c>
+      <c r="D149" s="1">
+        <v>105.46</v>
+      </c>
+      <c r="E149" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>16</v>
+      </c>
+      <c r="B150" t="s">
+        <v>40</v>
+      </c>
+      <c r="C150" s="1">
+        <v>73.22</v>
+      </c>
+      <c r="D150" s="1">
+        <v>78.58</v>
+      </c>
+      <c r="E150" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>33</v>
+      </c>
+      <c r="B151" t="s">
+        <v>40</v>
+      </c>
+      <c r="C151" s="1">
+        <v>123.84</v>
+      </c>
+      <c r="D151" s="1">
+        <v>106.44</v>
+      </c>
+      <c r="E151" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>34</v>
+      </c>
+      <c r="B152" t="s">
+        <v>40</v>
+      </c>
+      <c r="C152" s="1">
+        <v>106.44</v>
+      </c>
+      <c r="D152" s="1">
+        <v>123.84</v>
+      </c>
+      <c r="E152" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>17</v>
+      </c>
+      <c r="B153" t="s">
+        <v>40</v>
+      </c>
+      <c r="C153" s="1">
+        <v>122.4</v>
+      </c>
+      <c r="D153" s="1">
+        <v>113.94</v>
+      </c>
+      <c r="E153" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>18</v>
+      </c>
+      <c r="B154" t="s">
+        <v>40</v>
+      </c>
+      <c r="C154" s="1">
+        <v>78.58</v>
+      </c>
+      <c r="D154" s="1">
+        <v>73.22</v>
+      </c>
+      <c r="E154" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>19</v>
+      </c>
+      <c r="B155" t="s">
+        <v>40</v>
+      </c>
+      <c r="C155" s="1">
+        <v>97.62</v>
+      </c>
+      <c r="D155" s="1">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="E155" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>12</v>
+      </c>
+      <c r="B156" t="s">
+        <v>40</v>
+      </c>
+      <c r="C156" s="1">
+        <v>144.56</v>
+      </c>
+      <c r="D156" s="1">
+        <v>98.24</v>
+      </c>
+      <c r="E156" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>40</v>
+      </c>
+      <c r="C157" s="1">
+        <v>105.46</v>
+      </c>
+      <c r="D157" s="1">
+        <v>84.54</v>
+      </c>
+      <c r="E157" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-    </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-    </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-    </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-    </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-    </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-    </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-    </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-    </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-    </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-    </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
-    </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
-    </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-    </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-    </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
-    </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
-    </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
-    </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
-    </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
-    </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
-    </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
-    </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
-    </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
-    </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
-    </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
-    </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
-    </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
-    </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
-    </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
-    </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
-    </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
     </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
     </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
     </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
     </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
     </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
     </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
     </row>

--- a/FFL_Data.xlsx
+++ b/FFL_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axelrade\Downloads\FFL-Dash-2025-main\FFL-Dash-2025-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9E75DA-F3A0-46E1-AAD3-7BC590BBF0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18878BD-C34A-49CB-9ECF-7EAAC9D8A295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
+    <workbookView xWindow="5565" yWindow="3405" windowWidth="21600" windowHeight="11295" xr2:uid="{2A355A56-67D3-4EBE-9422-BA10374FFA74}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 Results" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="43">
   <si>
     <t>Points Against</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Stone Cold Kittles</t>
+  </si>
+  <si>
+    <t>Week 14</t>
   </si>
 </sst>
 </file>
@@ -2573,9 +2576,6 @@
       <c r="D146" s="1">
         <v>97.62</v>
       </c>
-      <c r="E146" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
@@ -2590,9 +2590,6 @@
       <c r="D147" s="1">
         <v>144.56</v>
       </c>
-      <c r="E147" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -2607,9 +2604,6 @@
       <c r="D148" s="1">
         <v>122.4</v>
       </c>
-      <c r="E148" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
@@ -2624,9 +2618,6 @@
       <c r="D149" s="1">
         <v>105.46</v>
       </c>
-      <c r="E149" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
@@ -2641,9 +2632,6 @@
       <c r="D150" s="1">
         <v>78.58</v>
       </c>
-      <c r="E150" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
@@ -2658,9 +2646,6 @@
       <c r="D151" s="1">
         <v>106.44</v>
       </c>
-      <c r="E151" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
@@ -2675,9 +2660,6 @@
       <c r="D152" s="1">
         <v>123.84</v>
       </c>
-      <c r="E152" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
@@ -2692,9 +2674,6 @@
       <c r="D153" s="1">
         <v>113.94</v>
       </c>
-      <c r="E153" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
@@ -2709,9 +2688,6 @@
       <c r="D154" s="1">
         <v>73.22</v>
       </c>
-      <c r="E154" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
@@ -2726,9 +2702,6 @@
       <c r="D155" s="1">
         <v>79.900000000000006</v>
       </c>
-      <c r="E155" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
@@ -2743,9 +2716,6 @@
       <c r="D156" s="1">
         <v>98.24</v>
       </c>
-      <c r="E156" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
@@ -2760,57 +2730,210 @@
       <c r="D157" s="1">
         <v>84.54</v>
       </c>
-      <c r="E157" t="s">
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" t="s">
+        <v>42</v>
+      </c>
+      <c r="C158" s="1">
+        <v>79.739999999999995</v>
+      </c>
+      <c r="D158" s="1">
+        <v>85.46</v>
+      </c>
+      <c r="E158" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>14</v>
+      </c>
+      <c r="B159" t="s">
+        <v>42</v>
+      </c>
+      <c r="C159" s="1">
+        <v>79.16</v>
+      </c>
+      <c r="D159" s="1">
+        <v>100.54</v>
+      </c>
+      <c r="E159" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>42</v>
+      </c>
+      <c r="C160" s="1">
+        <v>112.6</v>
+      </c>
+      <c r="D160" s="1">
+        <v>168.28</v>
+      </c>
+      <c r="E160" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>41</v>
+      </c>
+      <c r="B161" t="s">
+        <v>42</v>
+      </c>
+      <c r="C161" s="1">
+        <v>101.96</v>
+      </c>
+      <c r="D161" s="1">
+        <v>107.4</v>
+      </c>
+      <c r="E161" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>16</v>
+      </c>
+      <c r="B162" t="s">
+        <v>42</v>
+      </c>
+      <c r="C162" s="1">
+        <v>85.46</v>
+      </c>
+      <c r="D162" s="1">
+        <v>79.739999999999995</v>
+      </c>
+      <c r="E162" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>33</v>
+      </c>
+      <c r="B163" t="s">
+        <v>42</v>
+      </c>
+      <c r="C163" s="1">
+        <v>168.28</v>
+      </c>
+      <c r="D163" s="1">
+        <v>112.6</v>
+      </c>
+      <c r="E163" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>34</v>
+      </c>
+      <c r="B164" t="s">
+        <v>42</v>
+      </c>
+      <c r="C164" s="1">
+        <v>105.14</v>
+      </c>
+      <c r="D164" s="1">
+        <v>93.66</v>
+      </c>
+      <c r="E164" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>17</v>
+      </c>
+      <c r="B165" t="s">
+        <v>42</v>
+      </c>
+      <c r="C165" s="1">
+        <v>107.4</v>
+      </c>
+      <c r="D165" s="1">
+        <v>101.96</v>
+      </c>
+      <c r="E165" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>18</v>
+      </c>
+      <c r="B166" t="s">
+        <v>42</v>
+      </c>
+      <c r="C166" s="1">
+        <v>93.66</v>
+      </c>
+      <c r="D166" s="1">
+        <v>105.14</v>
+      </c>
+      <c r="E166" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>19</v>
+      </c>
+      <c r="B167" t="s">
+        <v>42</v>
+      </c>
+      <c r="C167" s="1">
+        <v>111.84</v>
+      </c>
+      <c r="D167" s="1">
+        <v>125.46</v>
+      </c>
+      <c r="E167" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>12</v>
+      </c>
+      <c r="B168" t="s">
+        <v>42</v>
+      </c>
+      <c r="C168" s="1">
+        <v>125.46</v>
+      </c>
+      <c r="D168" s="1">
+        <v>111.84</v>
+      </c>
+      <c r="E168" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>42</v>
+      </c>
+      <c r="C169" s="1">
+        <v>100.54</v>
+      </c>
+      <c r="D169" s="1">
+        <v>79.16</v>
+      </c>
+      <c r="E169" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
-    </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
-    </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
-    </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
-    </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
-    </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
-    </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
-    </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
-    </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
-    </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{657FD601-2028-0A4F-BA12-553C96356FC4}">
